--- a/SLSS V5/SLSS V5 Requirements.xlsx
+++ b/SLSS V5/SLSS V5 Requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\SLSS V5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E45D8B-BEB8-4E18-B24F-7500A43F8A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A29BB5A-0008-4A04-A30B-AA14578E7230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
   <si>
     <t>No</t>
   </si>
@@ -162,6 +162,12 @@
   </si>
   <si>
     <t>Check servo can spray bottle</t>
+  </si>
+  <si>
+    <t>Beams for holding substrate</t>
+  </si>
+  <si>
+    <t>two spaced beams which can wrap string around to hang the substrate from</t>
   </si>
 </sst>
 </file>
@@ -206,7 +212,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -264,13 +284,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8483FE8-83BD-4FD4-B975-1BFA0938C5BF}" name="Table1" displayName="Table1" ref="B14:E30" totalsRowShown="0" dataDxfId="4">
-  <autoFilter ref="B14:E30" xr:uid="{E8483FE8-83BD-4FD4-B975-1BFA0938C5BF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8483FE8-83BD-4FD4-B975-1BFA0938C5BF}" name="Table1" displayName="Table1" ref="B14:E32" totalsRowShown="0" dataDxfId="10">
+  <autoFilter ref="B14:E32" xr:uid="{E8483FE8-83BD-4FD4-B975-1BFA0938C5BF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{23CFA789-FF03-475E-AA4D-506F8D054482}" name="No." dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{D749B61C-74C6-4654-8692-591DC432ABF2}" name="Requirement" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{5BA96E61-7E13-4B39-B5AB-BBD799D8FADB}" name="Solution/design consideration" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{91BF3BD5-542B-4D71-AB6F-75648DBB12C6}" name="Agreed Consideration" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{23CFA789-FF03-475E-AA4D-506F8D054482}" name="No." dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{D749B61C-74C6-4654-8692-591DC432ABF2}" name="Requirement" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{5BA96E61-7E13-4B39-B5AB-BBD799D8FADB}" name="Solution/design consideration" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{91BF3BD5-542B-4D71-AB6F-75648DBB12C6}" name="Agreed Consideration" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -552,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B14:E30"/>
+  <dimension ref="B14:E32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="70.26953125" customWidth="1"/>
@@ -797,6 +817,26 @@
       <c r="E30" s="1" t="s">
         <v>10</v>
       </c>
+    </row>
+    <row r="31" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B31" s="1">
+        <v>17</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E15:E18">
@@ -811,11 +851,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E15:E30">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="No">
+  <conditionalFormatting sqref="E15:E32">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",E15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",E15)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -831,7 +871,7 @@
           <x14:formula1>
             <xm:f>Data!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E15:E30</xm:sqref>
+          <xm:sqref>E15:E32</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -917,10 +957,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E7">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",E3)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/SLSS V5/SLSS V5 Requirements.xlsx
+++ b/SLSS V5/SLSS V5 Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\SLSS V5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://npluk-my.sharepoint.com/personal/matthew_mcinnes_swaney_npl_co_uk/Documents/Documents/J/SLSS/SLSS V5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E45D8B-BEB8-4E18-B24F-7500A43F8A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{04E45D8B-BEB8-4E18-B24F-7500A43F8A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAF17032-2312-4E86-BD68-AE865977AD7C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -264,13 +264,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8483FE8-83BD-4FD4-B975-1BFA0938C5BF}" name="Table1" displayName="Table1" ref="B14:E30" totalsRowShown="0" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8483FE8-83BD-4FD4-B975-1BFA0938C5BF}" name="Table1" displayName="Table1" ref="B14:E30" totalsRowShown="0" dataDxfId="8">
   <autoFilter ref="B14:E30" xr:uid="{E8483FE8-83BD-4FD4-B975-1BFA0938C5BF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{23CFA789-FF03-475E-AA4D-506F8D054482}" name="No." dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{D749B61C-74C6-4654-8692-591DC432ABF2}" name="Requirement" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{5BA96E61-7E13-4B39-B5AB-BBD799D8FADB}" name="Solution/design consideration" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{91BF3BD5-542B-4D71-AB6F-75648DBB12C6}" name="Agreed Consideration" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{23CFA789-FF03-475E-AA4D-506F8D054482}" name="No." dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{D749B61C-74C6-4654-8692-591DC432ABF2}" name="Requirement" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{5BA96E61-7E13-4B39-B5AB-BBD799D8FADB}" name="Solution/design consideration" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{91BF3BD5-542B-4D71-AB6F-75648DBB12C6}" name="Agreed Consideration" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -553,14 +553,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B14:E30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="70.26953125" customWidth="1"/>
-    <col min="4" max="4" width="50.26953125" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="70.21875" customWidth="1"/>
+    <col min="4" max="4" width="50.21875" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>1</v>
       </c>
@@ -574,7 +575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>1</v>
       </c>
@@ -588,7 +589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>2</v>
       </c>
@@ -602,7 +603,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>3</v>
       </c>
@@ -616,7 +617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>4</v>
       </c>
@@ -630,7 +631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>5</v>
       </c>
@@ -644,7 +645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>6</v>
       </c>
@@ -658,7 +659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="1">
         <v>7</v>
       </c>
@@ -672,7 +673,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <v>8</v>
       </c>
@@ -686,7 +687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <v>9</v>
       </c>
@@ -700,7 +701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <v>10</v>
       </c>
@@ -714,7 +715,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B25" s="1">
         <v>11</v>
       </c>
@@ -728,7 +729,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
         <v>12</v>
       </c>
@@ -742,7 +743,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="1">
         <v>13</v>
       </c>
@@ -756,7 +757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B28" s="1">
         <v>14</v>
       </c>
@@ -770,7 +771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B29" s="1">
         <v>15</v>
       </c>
@@ -784,7 +785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="2:5" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B30" s="1">
         <v>16</v>
       </c>
@@ -842,15 +843,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D159CA1-4618-419F-BD7E-3A31B9353A67}">
   <dimension ref="B2:E7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.54296875" customWidth="1"/>
-    <col min="3" max="3" width="52.453125" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" customWidth="1"/>
+    <col min="3" max="3" width="52.44140625" customWidth="1"/>
     <col min="4" max="4" width="56" customWidth="1"/>
-    <col min="5" max="5" width="60.54296875" customWidth="1"/>
+    <col min="5" max="5" width="60.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -864,7 +865,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>1</v>
       </c>
@@ -872,7 +873,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" ht="23.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2</v>
       </c>
@@ -881,7 +882,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="2:5" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" ht="33.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>3</v>
       </c>
@@ -890,7 +891,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>4</v>
       </c>
@@ -899,7 +900,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
@@ -946,14 +947,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE3E2BE-3E97-4DBD-81DA-2792AF09A1BC}">
   <dimension ref="B2:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>0</v>
       </c>

--- a/SLSS V5/SLSS V5 Requirements.xlsx
+++ b/SLSS V5/SLSS V5 Requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\SLSS V5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A29BB5A-0008-4A04-A30B-AA14578E7230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C21136-2A8E-4D75-B304-3A610453EB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
   <si>
     <t>No</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>two spaced beams which can wrap string around to hang the substrate from</t>
+  </si>
+  <si>
+    <t>Check hole size of adafruit temperature and humidity sensor</t>
   </si>
 </sst>
 </file>
@@ -212,21 +215,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill>
@@ -284,13 +273,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8483FE8-83BD-4FD4-B975-1BFA0938C5BF}" name="Table1" displayName="Table1" ref="B14:E32" totalsRowShown="0" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8483FE8-83BD-4FD4-B975-1BFA0938C5BF}" name="Table1" displayName="Table1" ref="B14:E32" totalsRowShown="0" dataDxfId="8">
   <autoFilter ref="B14:E32" xr:uid="{E8483FE8-83BD-4FD4-B975-1BFA0938C5BF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{23CFA789-FF03-475E-AA4D-506F8D054482}" name="No." dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{D749B61C-74C6-4654-8692-591DC432ABF2}" name="Requirement" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{5BA96E61-7E13-4B39-B5AB-BBD799D8FADB}" name="Solution/design consideration" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{91BF3BD5-542B-4D71-AB6F-75648DBB12C6}" name="Agreed Consideration" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{23CFA789-FF03-475E-AA4D-506F8D054482}" name="No." dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{D749B61C-74C6-4654-8692-591DC432ABF2}" name="Requirement" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{5BA96E61-7E13-4B39-B5AB-BBD799D8FADB}" name="Solution/design consideration" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{91BF3BD5-542B-4D71-AB6F-75648DBB12C6}" name="Agreed Consideration" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -852,10 +841,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15:E32">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",E15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",E15)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -940,7 +929,12 @@
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="1"/>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="D7" s="1"/>
     </row>
   </sheetData>
@@ -957,10 +951,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E7">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",E3)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/SLSS V5/SLSS V5 Requirements.xlsx
+++ b/SLSS V5/SLSS V5 Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\SLSS V5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C21136-2A8E-4D75-B304-3A610453EB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B8BAFE-752D-420D-8A64-24DDE3F40815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
   <si>
     <t>No</t>
   </si>
@@ -171,6 +171,15 @@
   </si>
   <si>
     <t>Check hole size of adafruit temperature and humidity sensor</t>
+  </si>
+  <si>
+    <t>Check why when placing nuts mid 3d print, does it cause it to draw filament  over the hole and block it</t>
+  </si>
+  <si>
+    <t>Checked from CAD: 2.5mm</t>
+  </si>
+  <si>
+    <t>In progress: to be printed</t>
   </si>
 </sst>
 </file>
@@ -286,8 +295,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6A5FF8FF-A918-4EC8-8A0C-BF6077D88434}" name="Table13" displayName="Table13" ref="B2:E7" totalsRowShown="0">
-  <autoFilter ref="B2:E7" xr:uid="{6A5FF8FF-A918-4EC8-8A0C-BF6077D88434}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6A5FF8FF-A918-4EC8-8A0C-BF6077D88434}" name="Table13" displayName="Table13" ref="B2:E8" totalsRowShown="0">
+  <autoFilter ref="B2:E8" xr:uid="{6A5FF8FF-A918-4EC8-8A0C-BF6077D88434}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{4079217B-E63C-47A6-AF92-4BD015FCD872}" name="No."/>
     <tableColumn id="2" xr3:uid="{468656DC-60BD-490E-AE61-46E446FDDCA0}" name="Test"/>
@@ -870,7 +879,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D159CA1-4618-419F-BD7E-3A31B9353A67}">
-  <dimension ref="B2:E7"/>
+  <dimension ref="B2:E8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.54296875" customWidth="1"/>
@@ -926,7 +935,9 @@
       <c r="C6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="7" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7">
@@ -935,7 +946,20 @@
       <c r="C7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:E6">
@@ -950,7 +974,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E7">
+  <conditionalFormatting sqref="E3:E8">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",E3)))</formula>
     </cfRule>
@@ -969,7 +993,7 @@
           <x14:formula1>
             <xm:f>Data!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E7</xm:sqref>
+          <xm:sqref>E3:E8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/SLSS V5/SLSS V5 Requirements.xlsx
+++ b/SLSS V5/SLSS V5 Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\SLSS V5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://npluk-my.sharepoint.com/personal/james_edwards_npl_co_uk/Documents/Documents/SLSS/SLSS V5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B8BAFE-752D-420D-8A64-24DDE3F40815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{39B8BAFE-752D-420D-8A64-24DDE3F40815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A3DCA45-EF5E-49C6-B97A-BCA4EB3A0AF4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -179,7 +179,7 @@
     <t>Checked from CAD: 2.5mm</t>
   </si>
   <si>
-    <t>In progress: to be printed</t>
+    <t>Printed with bridging turned off, generally always does it but much worse ~2.8, also make holes wider as some nuts cant fit in. Make holes higher than 2.4mm. Nut width for m3 is 5.8mm but z height may be bad</t>
   </si>
 </sst>
 </file>
@@ -928,15 +928,12 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" ht="55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -950,7 +947,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" ht="58" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>6</v>
       </c>
@@ -960,10 +957,21 @@
       <c r="D8" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E3:E6">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="E3:E5 E7:E8">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",E3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",E3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E5 E8">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -972,14 +980,6 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E8">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",E3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -993,7 +993,7 @@
           <x14:formula1>
             <xm:f>Data!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E8</xm:sqref>
+          <xm:sqref>E3:E5 E7:E8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
